--- a/ConfigTables/收藏室配置.xlsx
+++ b/ConfigTables/收藏室配置.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品" sheetId="1" r:id="R350f667be5624de6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" r:id="Rb29f0f01a07945e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品" sheetId="1" r:id="R8a90401a024d4088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" r:id="R4bbc5da88a584f0d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,82 +71,82 @@
     <x:t xml:space="preserve">源岩</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">03</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">固源岩</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">04</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">精良</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">固源岩组</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">05</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">罕见</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">提纯源岩</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">说明</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">数据类型</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">可选值</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">数据说明</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">是否必填</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">示例</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">区分每一件藏品的固定编号</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">string</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">藏品稀有度</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">常见、普通、精良、罕见、稀有</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">玩家看到的中文名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">该模型中文名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">尽量参考原作</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">玩家看到的英文名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">该模型英文名称</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">否</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">03</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">固源岩</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">04</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">精良</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">固源岩组</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">05</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">罕见</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">提纯源岩</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">说明</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">数据类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">可选值</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">数据说明</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">是否必填</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">示例</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">区分每一件藏品的固定编号</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">string</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">藏品稀有度</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">常见、普通、精良、罕见、稀有</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">玩家看到的中文名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">该模型中文名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">尽量参考原作</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">玩家看到的英文名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">该模型英文名称</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">玩家看到的藏品介绍</x:t>
@@ -272,7 +272,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -289,6 +289,21 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="1"/>
@@ -565,7 +580,7 @@
         <x:v>#FFC802</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="13.800000190734863" customHeight="1">
+    <x:row r="3" ht="44" customHeight="1">
       <x:c r="A3" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -575,88 +590,110 @@
       <x:c r="C3" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
+      <x:c r="D3" s="1" t="str">
+        <x:v>ORIROCK</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>富含有机物的地表岩石，常见于源石挥发后的地区，便于采集，可用于强化与合成。</x:v>
+      </x:c>
       <x:c r="F3" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>20</x:v>
+      <x:c r="G3" s="1" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="H3" s="1"/>
-      <x:c r="I3" s="1"/>
+      <x:c r="I3" s="6"/>
       <x:c r="J3" s="1" t="str">
         <x:v>#A0A0A0</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="13.800000190734863" customHeight="1">
+    <x:row r="4" ht="44" customHeight="1">
       <x:c r="A4" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="C4" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
+      <x:c r="D4" s="1" t="str">
+        <x:v>ORIROCK CUBE</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>具有密集微孔的岩石固块，可吸附源石气体的分解物，常用于防护夹层及强化。</x:v>
+      </x:c>
       <x:c r="F4" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>20</x:v>
+      <x:c r="G4" s="1" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="H4" s="1"/>
-      <x:c r="I4" s="1"/>
+      <x:c r="I4" s="6" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockCubeDisplay.prefab</x:v>
+      </x:c>
       <x:c r="J4" s="1" t="str">
         <x:v>#DCE537</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="13.800000190734863" customHeight="1">
+    <x:row r="5" ht="44" customHeight="1">
       <x:c r="A5" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="C5" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D5" s="1"/>
-      <x:c r="E5" s="1"/>
+      <x:c r="D5" s="1" t="str">
+        <x:v>ORIROCK CLUSTER</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>固源岩压缩定型形成的岩石组合，也可自然形成。质地易碎，是强化与合成用料。</x:v>
+      </x:c>
       <x:c r="F5" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>20</x:v>
+      <x:c r="G5" s="1" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
-      <x:c r="I5" s="1"/>
+      <x:c r="I5" s="6" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockClusterDisplay.prefab</x:v>
+      </x:c>
       <x:c r="J5" s="1" t="str">
         <x:v>#00B3FD</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="13.800000190734863" customHeight="1">
+    <x:row r="6" ht="44" customHeight="1">
       <x:c r="A6" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="C6" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D6" s="1"/>
-      <x:c r="E6" s="1"/>
+      <x:c r="D6" s="1" t="str">
+        <x:v>ORIROCK CONCENTRATION</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>经高度提纯和规则切割得到的源岩，工艺与提纯成本较高，可用于强化及制作聚合剂。</x:v>
+      </x:c>
       <x:c r="F6" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>20</x:v>
+      <x:c r="G6" s="1" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="H6" s="1"/>
-      <x:c r="I6" s="1"/>
+      <x:c r="I6" s="6" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockConcentrationDisplay.prefab</x:v>
+      </x:c>
       <x:c r="J6" s="1" t="str">
         <x:v>#D6C5D6</x:v>
       </x:c>
@@ -691,65 +728,155 @@
         <x:v>#FFC802</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="1"/>
-      <x:c r="B8" s="1"/>
-      <x:c r="C8" s="1"/>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
-      <x:c r="H8" s="1"/>
-      <x:c r="I8" s="1"/>
-      <x:c r="J8" s="1"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="1"/>
-      <x:c r="B9" s="1"/>
-      <x:c r="C9" s="1"/>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
-      <x:c r="H9" s="1"/>
-      <x:c r="I9" s="1"/>
-      <x:c r="J9" s="1"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
-      <x:c r="H10" s="1"/>
-      <x:c r="I10" s="1"/>
-      <x:c r="J10" s="1"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="1"/>
-      <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
-      <x:c r="H11" s="1"/>
-      <x:c r="I11" s="1"/>
-      <x:c r="J11" s="1"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="1"/>
-      <x:c r="B12" s="1"/>
-      <x:c r="C12" s="1"/>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
-      <x:c r="H12" s="1"/>
-      <x:c r="I12" s="1"/>
-      <x:c r="J12" s="1"/>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="13" t="str">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>重相位对映体</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>REPHASIC ENANTIOMER</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>具备源石技艺适应性的实验性光功能材料，可承受高功率能量输出，用于高级强化。</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H8" s="14"/>
+      <x:c r="I8" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/RephasicEnantiomerDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>#FFC802</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="13" t="str">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>烧结核凝晶</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>NUCLEIC CRYSTAL SINTER</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>经高温工艺制成的精密晶体材料，可选择性吸附源石，用于源石器件加工与高级强化。</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H9" s="14"/>
+      <x:c r="I9" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/NucleicCrystalSinterDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="str">
+        <x:v>#FFC802</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="13" t="str">
+        <x:v>09</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>晶体电子单元</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>CRYSTALLINE ELECTRONIC UNIT</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>源石工业中的高精度电子单元，应用于施术设备与城际网络服务器，用于重要强化。</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H10" s="14"/>
+      <x:c r="I10" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/CrystallineElectronicUnitDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="str">
+        <x:v>#FFC802</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="13" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>双极纳米片</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>BIPOLAR NANOFLAKE</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>对附近源石反应敏感的精密装置，可提升武器与设备对源石的响应能力，用于高级强化。</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H11" s="14"/>
+      <x:c r="I11" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/BipolarNanoflakeDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="str">
+        <x:v>#FFC802</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="13" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>聚合剂</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>POLYMERIZATION PREPARATION</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>具有强粘接能力的液态工业材料，常用作精密装备的隔绝涂层，可阻断源石挥发。</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H12" s="14"/>
+      <x:c r="I12" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/PolymerizationPreparationDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="str">
+        <x:v>#FFC802</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="1"/>
@@ -3026,25 +3153,25 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="s">
+      <x:c r="H1" s="3" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="s">
+      <x:c r="J1" s="3" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="J1" s="3" t="s">
+      <x:c r="M1" s="3" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="M1" s="3" t="s">
+      <x:c r="P1" s="3" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="P1" s="3" t="s">
+      <x:c r="R1" s="3" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="R1" s="3" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3052,10 +3179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
         <x:v>15</x:v>
@@ -3069,13 +3196,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H5" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J5" s="3" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="H5" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J5" s="3" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="M5" s="3" t="str">
         <x:v>从低到高，对应 T1–T5</x:v>
@@ -3092,16 +3219,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H7" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H7" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J7" s="3" t="s">
+      <x:c r="M7" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="M7" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
         <x:v>15</x:v>
@@ -3115,19 +3242,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H9" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H9" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J9" s="3" t="s">
+      <x:c r="M9" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="P9" s="3" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="M9" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="P9" s="3" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>13</x:v>
@@ -3141,13 +3268,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>48</x:v>
@@ -3190,7 +3317,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3201,13 +3328,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
         <x:v>55</x:v>
@@ -3221,7 +3348,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H19" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J19" s="3" t="s">
         <x:v>57</x:v>
@@ -3230,7 +3357,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>59</x:v>
@@ -3253,7 +3380,7 @@
         <x:v>模型保持中性光照</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>61</x:v>
@@ -3501,13 +3628,13 @@
       <x:c r="Q41" s="9"/>
       <x:c r="R41" s="9"/>
     </x:row>
-    <x:row r="42">
+    <x:row r="42" ht="20" customHeight="1">
       <x:c r="A42" s="9" t="str">
         <x:v>分级来源</x:v>
       </x:c>
       <x:c r="B42" s="9"/>
-      <x:c r="C42" s="9" t="str">
-        <x:v>https://prts.wiki/w/D32钢</x:v>
+      <x:c r="C42" s="11" t="str">
+        <x:v>https://prts.wiki/w/道具一览；https://prts.wiki/w/D32钢</x:v>
       </x:c>
       <x:c r="D42" s="9"/>
       <x:c r="E42" s="9"/>

--- a/ConfigTables/收藏室配置.xlsx
+++ b/ConfigTables/收藏室配置.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品" sheetId="1" r:id="R8a90401a024d4088"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" r:id="R4bbc5da88a584f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品" sheetId="1" r:id="R3c0603ddbd634e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" r:id="R9680143710254c68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -69,15 +69,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">源岩</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">03</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">固源岩</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">04</x:t>
@@ -619,10 +610,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D4" s="1" t="str">
-        <x:v>ORIROCK CUBE</x:v>
+        <x:v>ORIROCK CLUSTER</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>具有密集微孔的岩石固块，可吸附源石气体的分解物，常用于防护夹层及强化。</x:v>
+        <x:v>固源岩压缩定型形成的岩石组合，也可自然形成。质地易碎，是强化与合成用料。</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
         <x:v>15</x:v>
@@ -632,10 +623,10 @@
       </x:c>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="6" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockCubeDisplay.prefab</x:v>
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockClusterDisplay.prefab</x:v>
       </x:c>
       <x:c r="J4" s="1" t="str">
-        <x:v>#DCE537</x:v>
+        <x:v>#00B3FD</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
@@ -649,10 +640,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D5" s="1" t="str">
-        <x:v>ORIROCK CLUSTER</x:v>
+        <x:v>ORIROCK CONCENTRATION</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>固源岩压缩定型形成的岩石组合，也可自然形成。质地易碎，是强化与合成用料。</x:v>
+        <x:v>经高度提纯和规则切割得到的源岩，工艺与提纯成本较高，可用于强化及制作聚合剂。</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
         <x:v>15</x:v>
@@ -662,87 +653,87 @@
       </x:c>
       <x:c r="H5" s="1"/>
       <x:c r="I5" s="6" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockClusterDisplay.prefab</x:v>
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockConcentrationDisplay.prefab</x:v>
       </x:c>
       <x:c r="J5" s="1" t="str">
-        <x:v>#00B3FD</x:v>
+        <x:v>#D6C5D6</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="44" customHeight="1">
-      <x:c r="A6" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="A6" s="5" t="str">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="str">
+        <x:v>D32钢</x:v>
       </x:c>
       <x:c r="D6" s="1" t="str">
-        <x:v>ORIROCK CONCENTRATION</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="str">
-        <x:v>经高度提纯和规则切割得到的源岩，工艺与提纯成本较高，可用于强化及制作聚合剂。</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>D32 STEEL</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="str">
+        <x:v>高强度的人造固态金属，可传导源石技艺，用于高级强化。</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="G6" s="1" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="H6" s="1"/>
-      <x:c r="I6" s="6" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockConcentrationDisplay.prefab</x:v>
+      <x:c r="I6" s="1" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/D32SteelDisplay.prefab</x:v>
       </x:c>
       <x:c r="J6" s="1" t="str">
-        <x:v>#D6C5D6</x:v>
+        <x:v>#FFC802</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
-      <x:c r="A7" s="5" t="str">
-        <x:v>06</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="str">
+      <x:c r="A7" s="13" t="str">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
         <x:v>稀有</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="str">
-        <x:v>D32钢</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="str">
-        <x:v>D32 STEEL</x:v>
-      </x:c>
-      <x:c r="E7" s="7" t="str">
-        <x:v>高强度的人造固态金属，可传导源石技艺，用于高级强化。</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="str">
+      <x:c r="C7" s="14" t="str">
+        <x:v>重相位对映体</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>REPHASIC ENANTIOMER</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>具备源石技艺适应性的实验性光功能材料，可承受高功率能量输出，用于高级强化。</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="G7" s="1" t="str">
+      <x:c r="G7" s="14" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="H7" s="1"/>
-      <x:c r="I7" s="1" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/D32SteelDisplay.prefab</x:v>
-      </x:c>
-      <x:c r="J7" s="1" t="str">
+      <x:c r="H7" s="14"/>
+      <x:c r="I7" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/RephasicEnantiomerDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
         <x:v>#FFC802</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" s="13" t="str">
-        <x:v>07</x:v>
+        <x:v>08</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
         <x:v>稀有</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>重相位对映体</x:v>
+        <x:v>烧结核凝晶</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
-        <x:v>REPHASIC ENANTIOMER</x:v>
+        <x:v>NUCLEIC CRYSTAL SINTER</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
-        <x:v>具备源石技艺适应性的实验性光功能材料，可承受高功率能量输出，用于高级强化。</x:v>
+        <x:v>经高温工艺制成的精密晶体材料，可选择性吸附源石，用于源石器件加工与高级强化。</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
         <x:v>是</x:v>
@@ -752,7 +743,7 @@
       </x:c>
       <x:c r="H8" s="14"/>
       <x:c r="I8" s="14" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/RephasicEnantiomerDisplay.prefab</x:v>
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/NucleicCrystalSinterDisplay.prefab</x:v>
       </x:c>
       <x:c r="J8" s="14" t="str">
         <x:v>#FFC802</x:v>
@@ -760,19 +751,19 @@
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" s="13" t="str">
-        <x:v>08</x:v>
+        <x:v>09</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
         <x:v>稀有</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>烧结核凝晶</x:v>
+        <x:v>晶体电子单元</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
-        <x:v>NUCLEIC CRYSTAL SINTER</x:v>
+        <x:v>CRYSTALLINE ELECTRONIC UNIT</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
-        <x:v>经高温工艺制成的精密晶体材料，可选择性吸附源石，用于源石器件加工与高级强化。</x:v>
+        <x:v>源石工业中的高精度电子单元，应用于施术设备与城际网络服务器，用于重要强化。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
         <x:v>是</x:v>
@@ -782,7 +773,7 @@
       </x:c>
       <x:c r="H9" s="14"/>
       <x:c r="I9" s="14" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/NucleicCrystalSinterDisplay.prefab</x:v>
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/CrystallineElectronicUnitDisplay.prefab</x:v>
       </x:c>
       <x:c r="J9" s="14" t="str">
         <x:v>#FFC802</x:v>
@@ -790,19 +781,19 @@
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" s="13" t="str">
-        <x:v>09</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
         <x:v>稀有</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>晶体电子单元</x:v>
+        <x:v>双极纳米片</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>CRYSTALLINE ELECTRONIC UNIT</x:v>
+        <x:v>BIPOLAR NANOFLAKE</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
-        <x:v>源石工业中的高精度电子单元，应用于施术设备与城际网络服务器，用于重要强化。</x:v>
+        <x:v>对附近源石反应敏感的精密装置，可提升武器与设备对源石的响应能力，用于高级强化。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
         <x:v>是</x:v>
@@ -812,7 +803,7 @@
       </x:c>
       <x:c r="H10" s="14"/>
       <x:c r="I10" s="14" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/CrystallineElectronicUnitDisplay.prefab</x:v>
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/BipolarNanoflakeDisplay.prefab</x:v>
       </x:c>
       <x:c r="J10" s="14" t="str">
         <x:v>#FFC802</x:v>
@@ -820,19 +811,19 @@
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" s="13" t="str">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>稀有</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>双极纳米片</x:v>
+        <x:v>聚合剂</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>BIPOLAR NANOFLAKE</x:v>
+        <x:v>POLYMERIZATION PREPARATION</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
-        <x:v>对附近源石反应敏感的精密装置，可提升武器与设备对源石的响应能力，用于高级强化。</x:v>
+        <x:v>具有强粘接能力的液态工业材料，常用作精密装备的隔绝涂层，可阻断源石挥发。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
         <x:v>是</x:v>
@@ -842,41 +833,23 @@
       </x:c>
       <x:c r="H11" s="14"/>
       <x:c r="I11" s="14" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/BipolarNanoflakeDisplay.prefab</x:v>
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/PolymerizationPreparationDisplay.prefab</x:v>
       </x:c>
       <x:c r="J11" s="14" t="str">
         <x:v>#FFC802</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
-      <x:c r="A12" s="13" t="str">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="14" t="str">
-        <x:v>稀有</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="str">
-        <x:v>聚合剂</x:v>
-      </x:c>
-      <x:c r="D12" s="14" t="str">
-        <x:v>POLYMERIZATION PREPARATION</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="str">
-        <x:v>具有强粘接能力的液态工业材料，常用作精密装备的隔绝涂层，可阻断源石挥发。</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="A12" s="13"/>
+      <x:c r="B12" s="14"/>
+      <x:c r="C12" s="14"/>
+      <x:c r="D12" s="14"/>
+      <x:c r="E12" s="14"/>
+      <x:c r="F12" s="14"/>
+      <x:c r="G12" s="14"/>
       <x:c r="H12" s="14"/>
-      <x:c r="I12" s="14" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/PolymerizationPreparationDisplay.prefab</x:v>
-      </x:c>
-      <x:c r="J12" s="14" t="str">
-        <x:v>#FFC802</x:v>
-      </x:c>
+      <x:c r="I12" s="14"/>
+      <x:c r="J12" s="14"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="1"/>
@@ -3153,25 +3126,25 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="s">
+      <x:c r="M1" s="3" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="s">
+      <x:c r="P1" s="3" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="J1" s="3" t="s">
+      <x:c r="R1" s="3" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="M1" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="P1" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="R1" s="3" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3179,10 +3152,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
         <x:v>15</x:v>
@@ -3196,13 +3169,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="M5" s="3" t="str">
         <x:v>从低到高，对应 T1–T5</x:v>
@@ -3219,16 +3192,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M7" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
         <x:v>15</x:v>
@@ -3242,19 +3215,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H9" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M9" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="P9" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="P9" s="3" t="s">
-        <x:v>45</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>13</x:v>
@@ -3265,19 +3238,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3285,13 +3258,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
         <x:v>15</x:v>
@@ -3305,19 +3278,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3325,19 +3298,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3345,22 +3318,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H19" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M19" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="P19" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="H19" s="3" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J19" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M19" s="3" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="P19" s="3" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="R19" s="3" t="s">
-        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3371,7 +3344,7 @@
         <x:v>稀有度决定背景色</x:v>
       </x:c>
       <x:c r="H21" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J21" s="3" t="str">
         <x:v>随稀有度自动生成</x:v>
@@ -3380,10 +3353,10 @@
         <x:v>模型保持中性光照</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -3391,27 +3364,27 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3512,7 +3485,7 @@
       <x:c r="K36" s="9"/>
       <x:c r="L36" s="9"/>
       <x:c r="M36" s="9" t="str">
-        <x:v>黄绿（固源岩）</x:v>
+        <x:v>黄绿</x:v>
       </x:c>
       <x:c r="N36" s="9"/>
       <x:c r="O36" s="9"/>

--- a/ConfigTables/收藏室配置.xlsx
+++ b/ConfigTables/收藏室配置.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品" sheetId="1" r:id="R350f667be5624de6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" r:id="Rb29f0f01a07945e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="藏品" sheetId="1" r:id="R3c0603ddbd634e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" r:id="R9680143710254c68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,82 +71,73 @@
     <x:t xml:space="preserve">源岩</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">04</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">精良</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">固源岩组</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">05</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">罕见</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">提纯源岩</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">说明</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">数据类型</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">可选值</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">数据说明</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">是否必填</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">示例</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">区分每一件藏品的固定编号</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">string</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">藏品稀有度</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">常见、普通、精良、罕见、稀有</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">玩家看到的中文名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">该模型中文名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">尽量参考原作</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">玩家看到的英文名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">该模型英文名称</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">否</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">03</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">固源岩</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">04</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">精良</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">固源岩组</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">05</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">罕见</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">提纯源岩</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">说明</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">数据类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">可选值</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">数据说明</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">是否必填</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">示例</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">区分每一件藏品的固定编号</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">string</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">藏品稀有度</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">常见、普通、精良、罕见、稀有</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">玩家看到的中文名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">该模型中文名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">尽量参考原作</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">玩家看到的英文名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">该模型英文名称</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">玩家看到的藏品介绍</x:t>
@@ -272,7 +263,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -289,6 +280,21 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="1"/>
@@ -565,7 +571,7 @@
         <x:v>#FFC802</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="13.800000190734863" customHeight="1">
+    <x:row r="3" ht="44" customHeight="1">
       <x:c r="A3" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -575,181 +581,275 @@
       <x:c r="C3" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
+      <x:c r="D3" s="1" t="str">
+        <x:v>ORIROCK</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>富含有机物的地表岩石，常见于源石挥发后的地区，便于采集，可用于强化与合成。</x:v>
+      </x:c>
       <x:c r="F3" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>20</x:v>
+      <x:c r="G3" s="1" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="H3" s="1"/>
-      <x:c r="I3" s="1"/>
+      <x:c r="I3" s="6"/>
       <x:c r="J3" s="1" t="str">
         <x:v>#A0A0A0</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="13.800000190734863" customHeight="1">
+    <x:row r="4" ht="44" customHeight="1">
       <x:c r="A4" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="C4" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
+      <x:c r="D4" s="1" t="str">
+        <x:v>ORIROCK CLUSTER</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>固源岩压缩定型形成的岩石组合，也可自然形成。质地易碎，是强化与合成用料。</x:v>
+      </x:c>
       <x:c r="F4" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>20</x:v>
+      <x:c r="G4" s="1" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="H4" s="1"/>
-      <x:c r="I4" s="1"/>
+      <x:c r="I4" s="6" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockClusterDisplay.prefab</x:v>
+      </x:c>
       <x:c r="J4" s="1" t="str">
-        <x:v>#DCE537</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="13.800000190734863" customHeight="1">
+        <x:v>#00B3FD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="44" customHeight="1">
       <x:c r="A5" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="C5" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D5" s="1"/>
-      <x:c r="E5" s="1"/>
+      <x:c r="D5" s="1" t="str">
+        <x:v>ORIROCK CONCENTRATION</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>经高度提纯和规则切割得到的源岩，工艺与提纯成本较高，可用于强化及制作聚合剂。</x:v>
+      </x:c>
       <x:c r="F5" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>20</x:v>
+      <x:c r="G5" s="1" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
-      <x:c r="I5" s="1"/>
+      <x:c r="I5" s="6" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/OrirockConcentrationDisplay.prefab</x:v>
+      </x:c>
       <x:c r="J5" s="1" t="str">
-        <x:v>#00B3FD</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="13.800000190734863" customHeight="1">
-      <x:c r="A6" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D6" s="1"/>
-      <x:c r="E6" s="1"/>
-      <x:c r="F6" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>#D6C5D6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="44" customHeight="1">
+      <x:c r="A6" s="5" t="str">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="str">
+        <x:v>D32钢</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="str">
+        <x:v>D32 STEEL</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="str">
+        <x:v>高强度的人造固态金属，可传导源石技艺，用于高级强化。</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="H6" s="1"/>
-      <x:c r="I6" s="1"/>
+      <x:c r="I6" s="1" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/D32SteelDisplay.prefab</x:v>
+      </x:c>
       <x:c r="J6" s="1" t="str">
-        <x:v>#D6C5D6</x:v>
+        <x:v>#FFC802</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
-      <x:c r="A7" s="5" t="str">
-        <x:v>06</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="str">
+      <x:c r="A7" s="13" t="str">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
         <x:v>稀有</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="str">
-        <x:v>D32钢</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="str">
-        <x:v>D32 STEEL</x:v>
-      </x:c>
-      <x:c r="E7" s="7" t="str">
-        <x:v>高强度的人造固态金属，可传导源石技艺，用于高级强化。</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="str">
+      <x:c r="C7" s="14" t="str">
+        <x:v>重相位对映体</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>REPHASIC ENANTIOMER</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>具备源石技艺适应性的实验性光功能材料，可承受高功率能量输出，用于高级强化。</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="G7" s="1" t="str">
+      <x:c r="G7" s="14" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="H7" s="1"/>
-      <x:c r="I7" s="1" t="str">
-        <x:v>Assets/YC/Presentation/Collection/Prefabs/D32SteelDisplay.prefab</x:v>
-      </x:c>
-      <x:c r="J7" s="1" t="str">
+      <x:c r="H7" s="14"/>
+      <x:c r="I7" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/RephasicEnantiomerDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
         <x:v>#FFC802</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="1"/>
-      <x:c r="B8" s="1"/>
-      <x:c r="C8" s="1"/>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
-      <x:c r="H8" s="1"/>
-      <x:c r="I8" s="1"/>
-      <x:c r="J8" s="1"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="1"/>
-      <x:c r="B9" s="1"/>
-      <x:c r="C9" s="1"/>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
-      <x:c r="H9" s="1"/>
-      <x:c r="I9" s="1"/>
-      <x:c r="J9" s="1"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
-      <x:c r="H10" s="1"/>
-      <x:c r="I10" s="1"/>
-      <x:c r="J10" s="1"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="1"/>
-      <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
-      <x:c r="H11" s="1"/>
-      <x:c r="I11" s="1"/>
-      <x:c r="J11" s="1"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="1"/>
-      <x:c r="B12" s="1"/>
-      <x:c r="C12" s="1"/>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
-      <x:c r="H12" s="1"/>
-      <x:c r="I12" s="1"/>
-      <x:c r="J12" s="1"/>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="13" t="str">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>烧结核凝晶</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>NUCLEIC CRYSTAL SINTER</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>经高温工艺制成的精密晶体材料，可选择性吸附源石，用于源石器件加工与高级强化。</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H8" s="14"/>
+      <x:c r="I8" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/NucleicCrystalSinterDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>#FFC802</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="13" t="str">
+        <x:v>09</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>晶体电子单元</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>CRYSTALLINE ELECTRONIC UNIT</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>源石工业中的高精度电子单元，应用于施术设备与城际网络服务器，用于重要强化。</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H9" s="14"/>
+      <x:c r="I9" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/CrystallineElectronicUnitDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="str">
+        <x:v>#FFC802</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="13" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>双极纳米片</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>BIPOLAR NANOFLAKE</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>对附近源石反应敏感的精密装置，可提升武器与设备对源石的响应能力，用于高级强化。</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H10" s="14"/>
+      <x:c r="I10" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/BipolarNanoflakeDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="str">
+        <x:v>#FFC802</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="13" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>稀有</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>聚合剂</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>POLYMERIZATION PREPARATION</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>具有强粘接能力的液态工业材料，常用作精密装备的隔绝涂层，可阻断源石挥发。</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H11" s="14"/>
+      <x:c r="I11" s="14" t="str">
+        <x:v>Assets/YC/Presentation/Collection/Prefabs/PolymerizationPreparationDisplay.prefab</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="str">
+        <x:v>#FFC802</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="13"/>
+      <x:c r="B12" s="14"/>
+      <x:c r="C12" s="14"/>
+      <x:c r="D12" s="14"/>
+      <x:c r="E12" s="14"/>
+      <x:c r="F12" s="14"/>
+      <x:c r="G12" s="14"/>
+      <x:c r="H12" s="14"/>
+      <x:c r="I12" s="14"/>
+      <x:c r="J12" s="14"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="1"/>
@@ -3026,25 +3126,25 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="M1" s="3" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="s">
+      <x:c r="P1" s="3" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="s">
+      <x:c r="R1" s="3" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="M1" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="P1" s="3" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="R1" s="3" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3052,10 +3152,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
         <x:v>15</x:v>
@@ -3069,13 +3169,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="M5" s="3" t="str">
         <x:v>从低到高，对应 T1–T5</x:v>
@@ -3092,16 +3192,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="J7" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="M7" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
         <x:v>15</x:v>
@@ -3115,19 +3215,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H9" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M9" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>13</x:v>
@@ -3138,19 +3238,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3158,13 +3258,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
         <x:v>15</x:v>
@@ -3178,19 +3278,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3198,19 +3298,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3218,22 +3318,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H19" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M19" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="P19" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="H19" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J19" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M19" s="3" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="P19" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="R19" s="3" t="s">
-        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3244,7 +3344,7 @@
         <x:v>稀有度决定背景色</x:v>
       </x:c>
       <x:c r="H21" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J21" s="3" t="str">
         <x:v>随稀有度自动生成</x:v>
@@ -3253,10 +3353,10 @@
         <x:v>模型保持中性光照</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -3264,27 +3364,27 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3385,7 +3485,7 @@
       <x:c r="K36" s="9"/>
       <x:c r="L36" s="9"/>
       <x:c r="M36" s="9" t="str">
-        <x:v>黄绿（固源岩）</x:v>
+        <x:v>黄绿</x:v>
       </x:c>
       <x:c r="N36" s="9"/>
       <x:c r="O36" s="9"/>
@@ -3501,13 +3601,13 @@
       <x:c r="Q41" s="9"/>
       <x:c r="R41" s="9"/>
     </x:row>
-    <x:row r="42">
+    <x:row r="42" ht="20" customHeight="1">
       <x:c r="A42" s="9" t="str">
         <x:v>分级来源</x:v>
       </x:c>
       <x:c r="B42" s="9"/>
-      <x:c r="C42" s="9" t="str">
-        <x:v>https://prts.wiki/w/D32钢</x:v>
+      <x:c r="C42" s="11" t="str">
+        <x:v>https://prts.wiki/w/道具一览；https://prts.wiki/w/D32钢</x:v>
       </x:c>
       <x:c r="D42" s="9"/>
       <x:c r="E42" s="9"/>
